--- a/lucas/import_data/utility/landscape/excel/land_cover_genus.xlsx
+++ b/lucas/import_data/utility/landscape/excel/land_cover_genus.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="232">
   <si>
     <t xml:space="preserve">landcover_family_id__landcover_family_name</t>
   </si>
@@ -689,6 +689,24 @@
   </si>
   <si>
     <t xml:space="preserve">Fen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salt marshes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salt marshes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salines</t>
   </si>
   <si>
     <t xml:space="preserve">unclassified</t>
@@ -712,6 +730,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -771,8 +790,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -796,37 +819,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -899,1036 +922,1064 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D75"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.51"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="0" t="s">
+      <c r="A15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="0" t="s">
+      <c r="A16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="0" t="s">
+      <c r="A17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="0" t="s">
+      <c r="A18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="0" t="s">
+      <c r="A19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="0" t="s">
+      <c r="A20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="0" t="s">
+      <c r="A21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="0" t="s">
+      <c r="A22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="0" t="s">
+      <c r="A23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="0" t="s">
+      <c r="A24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="0" t="s">
+      <c r="A25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="0" t="s">
+      <c r="A26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="0" t="s">
+      <c r="A27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="0" t="s">
+      <c r="A28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="0" t="s">
+      <c r="A29" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="0" t="s">
+      <c r="A30" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" s="0" t="s">
+      <c r="A31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="0" t="s">
+      <c r="A32" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="0" t="s">
+      <c r="A33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="0" t="s">
+      <c r="A34" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="0" t="s">
+      <c r="A35" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="0" t="s">
+      <c r="A36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="0" t="s">
+      <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="0" t="s">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="0" t="s">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40" s="0" t="s">
+      <c r="A40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="0" t="s">
+      <c r="A41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="0" t="s">
+      <c r="A42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="1" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="0" t="s">
+      <c r="A43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C43" s="0" t="s">
+      <c r="C43" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="0" t="s">
+      <c r="A44" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C44" s="0" t="s">
+      <c r="C44" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" s="0" t="s">
+      <c r="A45" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C45" s="0" t="s">
+      <c r="C45" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="1" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" s="0" t="s">
+      <c r="A46" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C46" s="0" t="s">
+      <c r="C46" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="0" t="s">
+      <c r="D46" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="0" t="s">
+      <c r="A47" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C47" s="0" t="s">
+      <c r="C47" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D47" s="0" t="s">
+      <c r="D47" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C48" s="0" t="s">
+      <c r="C48" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D48" s="0" t="s">
+      <c r="D48" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C49" s="0" t="s">
+      <c r="C49" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D49" s="0" t="s">
+      <c r="D49" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C50" s="0" t="s">
+      <c r="C50" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D50" s="0" t="s">
+      <c r="D50" s="1" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C51" s="0" t="s">
+      <c r="C51" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D51" s="0" t="s">
+      <c r="D51" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C52" s="0" t="s">
+      <c r="C52" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D52" s="0" t="s">
+      <c r="D52" s="1" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C53" s="0" t="s">
+      <c r="C53" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D53" s="0" t="s">
+      <c r="D53" s="1" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C54" s="0" t="s">
+      <c r="C54" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D54" s="0" t="s">
+      <c r="D54" s="1" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C55" s="0" t="s">
+      <c r="C55" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D55" s="0" t="s">
+      <c r="D55" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="B56" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C56" s="0" t="s">
+      <c r="C56" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D56" s="0" t="s">
+      <c r="D56" s="1" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C57" s="0" t="s">
+      <c r="C57" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D57" s="0" t="s">
+      <c r="D57" s="1" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C58" s="0" t="s">
+      <c r="C58" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D58" s="0" t="s">
+      <c r="D58" s="1" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C59" s="0" t="s">
+      <c r="C59" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D59" s="0" t="s">
+      <c r="D59" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C60" s="0" t="s">
+      <c r="C60" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D60" s="0" t="s">
+      <c r="D60" s="1" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C61" s="0" t="s">
+      <c r="C61" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D61" s="0" t="s">
+      <c r="D61" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C62" s="0" t="s">
+      <c r="C62" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D62" s="0" t="s">
+      <c r="D62" s="1" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C63" s="0" t="s">
+      <c r="C63" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D63" s="0" t="s">
+      <c r="D63" s="1" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="B64" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C64" s="0" t="s">
+      <c r="C64" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D64" s="0" t="s">
+      <c r="D64" s="1" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="B65" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C65" s="0" t="s">
+      <c r="C65" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D65" s="0" t="s">
+      <c r="D65" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C66" s="0" t="s">
+      <c r="C66" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D66" s="0" t="s">
+      <c r="D66" s="1" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C67" s="0" t="s">
+      <c r="C67" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D67" s="0" t="s">
+      <c r="D67" s="1" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C68" s="0" t="s">
+      <c r="C68" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D68" s="0" t="s">
+      <c r="D68" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C69" s="0" t="s">
+      <c r="C69" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D69" s="0" t="s">
+      <c r="D69" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C70" s="0" t="s">
+      <c r="C70" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D70" s="0" t="s">
+      <c r="D70" s="1" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C71" s="0" t="s">
+      <c r="C71" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="D71" s="0" t="s">
+      <c r="D71" s="1" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="B72" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C72" s="0" t="s">
+      <c r="C72" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D72" s="0" t="s">
+      <c r="D72" s="1" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B73" s="0" t="s">
-        <v>223</v>
-      </c>
-      <c r="C73" s="0" t="s">
+      <c r="C73" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D73" s="0" t="s">
+      <c r="D73" s="1" t="s">
         <v>225</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/lucas/import_data/utility/landscape/excel/land_cover_genus.xlsx
+++ b/lucas/import_data/utility/landscape/excel/land_cover_genus.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="283">
   <si>
     <t xml:space="preserve">landcover_family_id__landcover_family_name</t>
   </si>
@@ -34,6 +34,9 @@
     <t xml:space="preserve">display_name</t>
   </si>
   <si>
+    <t xml:space="preserve">tag</t>
+  </si>
+  <si>
     <t xml:space="preserve">city/town area</t>
   </si>
   <si>
@@ -46,6 +49,9 @@
     <t xml:space="preserve">Core city/town areas</t>
   </si>
   <si>
+    <t xml:space="preserve">city-center</t>
+  </si>
+  <si>
     <t xml:space="preserve">artificial land</t>
   </si>
   <si>
@@ -58,6 +64,9 @@
     <t xml:space="preserve">Greenhouses</t>
   </si>
   <si>
+    <t xml:space="preserve">greehouse</t>
+  </si>
+  <si>
     <t xml:space="preserve">villages</t>
   </si>
   <si>
@@ -67,6 +76,9 @@
     <t xml:space="preserve">Villages</t>
   </si>
   <si>
+    <t xml:space="preserve">village</t>
+  </si>
+  <si>
     <t xml:space="preserve">scattered buildings</t>
   </si>
   <si>
@@ -76,6 +88,9 @@
     <t xml:space="preserve">Scattered buildings</t>
   </si>
   <si>
+    <t xml:space="preserve">buidling</t>
+  </si>
+  <si>
     <t xml:space="preserve">railways</t>
   </si>
   <si>
@@ -85,6 +100,9 @@
     <t xml:space="preserve">Railways</t>
   </si>
   <si>
+    <t xml:space="preserve">railway</t>
+  </si>
+  <si>
     <t xml:space="preserve">motorways and major roads</t>
   </si>
   <si>
@@ -94,6 +112,9 @@
     <t xml:space="preserve">Motorways and major roads</t>
   </si>
   <si>
+    <t xml:space="preserve">major-roads</t>
+  </si>
+  <si>
     <t xml:space="preserve">other roads and associated areas</t>
   </si>
   <si>
@@ -103,6 +124,9 @@
     <t xml:space="preserve">Other roads and associated areas</t>
   </si>
   <si>
+    <t xml:space="preserve">minor-road</t>
+  </si>
+  <si>
     <t xml:space="preserve">airports</t>
   </si>
   <si>
@@ -112,6 +136,9 @@
     <t xml:space="preserve">Airports</t>
   </si>
   <si>
+    <t xml:space="preserve">airport</t>
+  </si>
+  <si>
     <t xml:space="preserve">harbours</t>
   </si>
   <si>
@@ -121,6 +148,9 @@
     <t xml:space="preserve">Harbours</t>
   </si>
   <si>
+    <t xml:space="preserve">harbour</t>
+  </si>
+  <si>
     <t xml:space="preserve">mines and pits</t>
   </si>
   <si>
@@ -130,6 +160,9 @@
     <t xml:space="preserve">Mines and pits</t>
   </si>
   <si>
+    <t xml:space="preserve">mines-pits</t>
+  </si>
+  <si>
     <t xml:space="preserve">dump sites</t>
   </si>
   <si>
@@ -139,6 +172,9 @@
     <t xml:space="preserve">Dump sites</t>
   </si>
   <si>
+    <t xml:space="preserve">dump</t>
+  </si>
+  <si>
     <t xml:space="preserve">construction sites</t>
   </si>
   <si>
@@ -148,6 +184,9 @@
     <t xml:space="preserve">Construction sites</t>
   </si>
   <si>
+    <t xml:space="preserve">construction</t>
+  </si>
+  <si>
     <t xml:space="preserve">green urban areas</t>
   </si>
   <si>
@@ -157,6 +196,9 @@
     <t xml:space="preserve">Green urban areas</t>
   </si>
   <si>
+    <t xml:space="preserve">green-urban</t>
+  </si>
+  <si>
     <t xml:space="preserve">cultivated cropland</t>
   </si>
   <si>
@@ -169,6 +211,9 @@
     <t xml:space="preserve">Common wheat</t>
   </si>
   <si>
+    <t xml:space="preserve">wheat</t>
+  </si>
+  <si>
     <t xml:space="preserve">durum wheat</t>
   </si>
   <si>
@@ -178,6 +223,9 @@
     <t xml:space="preserve">Durum wheat</t>
   </si>
   <si>
+    <t xml:space="preserve">durum-wheat</t>
+  </si>
+  <si>
     <t xml:space="preserve">barley</t>
   </si>
   <si>
@@ -241,6 +289,9 @@
     <t xml:space="preserve">Other cereals</t>
   </si>
   <si>
+    <t xml:space="preserve">other-cereals</t>
+  </si>
+  <si>
     <t xml:space="preserve">root crops</t>
   </si>
   <si>
@@ -250,6 +301,9 @@
     <t xml:space="preserve">Root crops</t>
   </si>
   <si>
+    <t xml:space="preserve">root-crops</t>
+  </si>
+  <si>
     <t xml:space="preserve">potatoes</t>
   </si>
   <si>
@@ -268,6 +322,9 @@
     <t xml:space="preserve">Sugar beet</t>
   </si>
   <si>
+    <t xml:space="preserve">sugar-beet</t>
+  </si>
+  <si>
     <t xml:space="preserve">other root crops</t>
   </si>
   <si>
@@ -277,6 +334,9 @@
     <t xml:space="preserve">Other root crops</t>
   </si>
   <si>
+    <t xml:space="preserve">other-root-crops</t>
+  </si>
+  <si>
     <t xml:space="preserve">sunflower</t>
   </si>
   <si>
@@ -295,6 +355,9 @@
     <t xml:space="preserve">Rape and turnip seeds</t>
   </si>
   <si>
+    <t xml:space="preserve">rape-turnip</t>
+  </si>
+  <si>
     <t xml:space="preserve">soya</t>
   </si>
   <si>
@@ -322,6 +385,9 @@
     <t xml:space="preserve">Other fibre oleaginous crops</t>
   </si>
   <si>
+    <t xml:space="preserve">other-fibre-olea</t>
+  </si>
+  <si>
     <t xml:space="preserve">tobacco</t>
   </si>
   <si>
@@ -340,6 +406,9 @@
     <t xml:space="preserve">Other non-permanent industrial crops</t>
   </si>
   <si>
+    <t xml:space="preserve">other-temp-industrial-crop</t>
+  </si>
+  <si>
     <t xml:space="preserve">fallow land</t>
   </si>
   <si>
@@ -349,6 +418,9 @@
     <t xml:space="preserve">Fallow land</t>
   </si>
   <si>
+    <t xml:space="preserve">fallow-land</t>
+  </si>
+  <si>
     <t xml:space="preserve">other industrial crops</t>
   </si>
   <si>
@@ -358,6 +430,9 @@
     <t xml:space="preserve">Other industrial crops</t>
   </si>
   <si>
+    <t xml:space="preserve">other-industrial-crops</t>
+  </si>
+  <si>
     <t xml:space="preserve">dry pulses</t>
   </si>
   <si>
@@ -367,6 +442,9 @@
     <t xml:space="preserve">Dry pulses</t>
   </si>
   <si>
+    <t xml:space="preserve">dry-pulses</t>
+  </si>
+  <si>
     <t xml:space="preserve">tomatoes</t>
   </si>
   <si>
@@ -385,6 +463,9 @@
     <t xml:space="preserve">Other fresh vegetables</t>
   </si>
   <si>
+    <t xml:space="preserve">other-vegetables</t>
+  </si>
+  <si>
     <t xml:space="preserve">floriculture and ornamental plants</t>
   </si>
   <si>
@@ -394,6 +475,9 @@
     <t xml:space="preserve">Floriculture and ornamental plants</t>
   </si>
   <si>
+    <t xml:space="preserve">floriculture</t>
+  </si>
+  <si>
     <t xml:space="preserve">strawberries</t>
   </si>
   <si>
@@ -433,6 +517,9 @@
     <t xml:space="preserve">Leguminous fodder</t>
   </si>
   <si>
+    <t xml:space="preserve">leguminous-fodder</t>
+  </si>
+  <si>
     <t xml:space="preserve">mix of cereals</t>
   </si>
   <si>
@@ -442,6 +529,9 @@
     <t xml:space="preserve">Mix of cereals</t>
   </si>
   <si>
+    <t xml:space="preserve">mix-of-cereals</t>
+  </si>
+  <si>
     <t xml:space="preserve">temporary grassland</t>
   </si>
   <si>
@@ -451,6 +541,9 @@
     <t xml:space="preserve">Temporary grassland</t>
   </si>
   <si>
+    <t xml:space="preserve">temp-grassland</t>
+  </si>
+  <si>
     <t xml:space="preserve">agroforestry</t>
   </si>
   <si>
@@ -463,6 +556,9 @@
     <t xml:space="preserve">Apple fruit</t>
   </si>
   <si>
+    <t xml:space="preserve">apple</t>
+  </si>
+  <si>
     <t xml:space="preserve">pear fruit</t>
   </si>
   <si>
@@ -472,6 +568,9 @@
     <t xml:space="preserve">Pear fruit</t>
   </si>
   <si>
+    <t xml:space="preserve">pear</t>
+  </si>
+  <si>
     <t xml:space="preserve">cherry fruit</t>
   </si>
   <si>
@@ -481,6 +580,9 @@
     <t xml:space="preserve">Cherry fruit</t>
   </si>
   <si>
+    <t xml:space="preserve">cherry</t>
+  </si>
+  <si>
     <t xml:space="preserve">nuts trees</t>
   </si>
   <si>
@@ -490,6 +592,9 @@
     <t xml:space="preserve">Nuts trees</t>
   </si>
   <si>
+    <t xml:space="preserve">nuts</t>
+  </si>
+  <si>
     <t xml:space="preserve">other fruit trees and berries</t>
   </si>
   <si>
@@ -499,6 +604,9 @@
     <t xml:space="preserve">Other fruit trees and berries</t>
   </si>
   <si>
+    <t xml:space="preserve">other-fruit</t>
+  </si>
+  <si>
     <t xml:space="preserve">oranges</t>
   </si>
   <si>
@@ -517,6 +625,9 @@
     <t xml:space="preserve">Other citrus fruit</t>
   </si>
   <si>
+    <t xml:space="preserve">citrus-fruit</t>
+  </si>
+  <si>
     <t xml:space="preserve">olive groves</t>
   </si>
   <si>
@@ -526,6 +637,9 @@
     <t xml:space="preserve">Olive groves</t>
   </si>
   <si>
+    <t xml:space="preserve">olive</t>
+  </si>
+  <si>
     <t xml:space="preserve">vineyards</t>
   </si>
   <si>
@@ -553,6 +667,9 @@
     <t xml:space="preserve">Permanent industrial crops</t>
   </si>
   <si>
+    <t xml:space="preserve">perm-industrial-crop</t>
+  </si>
+  <si>
     <t xml:space="preserve">other permanent crops</t>
   </si>
   <si>
@@ -562,6 +679,9 @@
     <t xml:space="preserve">Other permanent crops</t>
   </si>
   <si>
+    <t xml:space="preserve">other-permanent-crop</t>
+  </si>
+  <si>
     <t xml:space="preserve">coniferous woodland</t>
   </si>
   <si>
@@ -574,6 +694,9 @@
     <t xml:space="preserve">Spruce dominated coniferous woodland</t>
   </si>
   <si>
+    <t xml:space="preserve">spruce-woodl</t>
+  </si>
+  <si>
     <t xml:space="preserve">pine dominated coniferous woodland</t>
   </si>
   <si>
@@ -583,6 +706,9 @@
     <t xml:space="preserve">Pine dominated coniferous woodland</t>
   </si>
   <si>
+    <t xml:space="preserve">pine-woodl</t>
+  </si>
+  <si>
     <t xml:space="preserve">other coniferous woodland</t>
   </si>
   <si>
@@ -592,6 +718,9 @@
     <t xml:space="preserve">Other coniferous woodland</t>
   </si>
   <si>
+    <t xml:space="preserve">other-conif-woodl</t>
+  </si>
+  <si>
     <t xml:space="preserve">mixed woodland</t>
   </si>
   <si>
@@ -604,6 +733,9 @@
     <t xml:space="preserve">Spruce dominated mixed woodland</t>
   </si>
   <si>
+    <t xml:space="preserve">spruce-mix-woodl</t>
+  </si>
+  <si>
     <t xml:space="preserve">pine dominated mixed woodland</t>
   </si>
   <si>
@@ -613,6 +745,9 @@
     <t xml:space="preserve">Pine dominated mixed woodland</t>
   </si>
   <si>
+    <t xml:space="preserve">pine-mix-woodl</t>
+  </si>
+  <si>
     <t xml:space="preserve">other mixed woodland</t>
   </si>
   <si>
@@ -622,6 +757,9 @@
     <t xml:space="preserve">Other mixed woodland</t>
   </si>
   <si>
+    <t xml:space="preserve">other-mixed-woodl</t>
+  </si>
+  <si>
     <t xml:space="preserve">water</t>
   </si>
   <si>
@@ -634,6 +772,9 @@
     <t xml:space="preserve">Inland running water</t>
   </si>
   <si>
+    <t xml:space="preserve">running-water</t>
+  </si>
+  <si>
     <t xml:space="preserve">inland standing water</t>
   </si>
   <si>
@@ -643,6 +784,9 @@
     <t xml:space="preserve">Inland standing water</t>
   </si>
   <si>
+    <t xml:space="preserve">standing-water</t>
+  </si>
+  <si>
     <t xml:space="preserve">sea and ocean</t>
   </si>
   <si>
@@ -652,6 +796,9 @@
     <t xml:space="preserve">Sea and ocean</t>
   </si>
   <si>
+    <t xml:space="preserve">sea-ocean</t>
+  </si>
+  <si>
     <t xml:space="preserve">estuary</t>
   </si>
   <si>
@@ -700,6 +847,9 @@
     <t xml:space="preserve">Salt marshes</t>
   </si>
   <si>
+    <t xml:space="preserve">salt-marsh</t>
+  </si>
+  <si>
     <t xml:space="preserve">salines</t>
   </si>
   <si>
@@ -707,6 +857,9 @@
   </si>
   <si>
     <t xml:space="preserve">Salines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">saline</t>
   </si>
   <si>
     <t xml:space="preserve">unclassified</t>
@@ -922,7 +1075,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.12"/>
@@ -945,1041 +1098,1266 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>48</v>
+        <v>62</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>54</v>
+        <v>70</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>60</v>
+        <v>76</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>66</v>
+        <v>82</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>69</v>
+        <v>85</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>75</v>
+        <v>92</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>78</v>
+        <v>96</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>81</v>
+        <v>99</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>84</v>
+        <v>103</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>87</v>
+        <v>107</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>90</v>
+        <v>110</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>93</v>
+        <v>114</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>96</v>
+        <v>117</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>99</v>
+        <v>120</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>102</v>
+        <v>124</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>105</v>
+        <v>127</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>108</v>
+        <v>131</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>111</v>
+        <v>135</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>114</v>
+        <v>139</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>117</v>
+        <v>143</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>120</v>
+        <v>146</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>123</v>
+        <v>150</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>126</v>
+        <v>154</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>84</v>
+        <v>103</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>130</v>
+        <v>158</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>133</v>
+        <v>161</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>136</v>
+        <v>164</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>139</v>
+        <v>168</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>142</v>
+        <v>172</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>146</v>
+        <v>177</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>149</v>
+        <v>181</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>152</v>
+        <v>185</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>155</v>
+        <v>189</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>158</v>
+        <v>193</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>161</v>
+        <v>197</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>164</v>
+        <v>200</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>166</v>
+        <v>203</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>167</v>
+        <v>204</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>170</v>
+        <v>208</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>173</v>
+        <v>211</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>175</v>
+        <v>213</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>176</v>
+        <v>214</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>179</v>
+        <v>218</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>182</v>
+        <v>222</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>183</v>
+        <v>223</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>185</v>
+        <v>226</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>186</v>
+        <v>227</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>189</v>
+        <v>231</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>190</v>
+        <v>233</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>192</v>
+        <v>235</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>193</v>
+        <v>236</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>190</v>
+        <v>233</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>194</v>
+        <v>238</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>195</v>
+        <v>239</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>196</v>
+        <v>240</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>190</v>
+        <v>233</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>197</v>
+        <v>242</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>198</v>
+        <v>243</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>199</v>
+        <v>244</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>202</v>
+        <v>248</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>203</v>
+        <v>249</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>204</v>
+        <v>251</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>206</v>
+        <v>253</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>207</v>
+        <v>255</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>208</v>
+        <v>256</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>209</v>
+        <v>257</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>210</v>
+        <v>259</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>211</v>
+        <v>260</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>212</v>
+        <v>261</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>214</v>
+        <v>263</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>215</v>
+        <v>264</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>216</v>
+        <v>265</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>217</v>
+        <v>266</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>218</v>
+        <v>267</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>219</v>
+        <v>268</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>220</v>
+        <v>269</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>221</v>
+        <v>270</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>222</v>
+        <v>271</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>223</v>
+        <v>272</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>225</v>
+        <v>274</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>226</v>
+        <v>276</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>227</v>
+        <v>277</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>228</v>
+        <v>278</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>229</v>
+        <v>280</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>229</v>
+        <v>280</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>231</v>
+        <v>282</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>
